--- a/picha12mo/data_dict_en.xlsx
+++ b/picha12mo/data_dict_en.xlsx
@@ -15,17 +15,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Codes!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$K$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$K$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Notes!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Overview!$A$3:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Relationships!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Relationships!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="399">
   <si>
     <t>Table</t>
   </si>
@@ -105,7 +105,7 @@
     <t>PiCha Tea House — Data Dictionary (picha12mo.duckdb)</t>
   </si>
   <si>
-    <t>2026-01-01 to 2026-12-31 · 7 tables · 99 columns</t>
+    <t>2026-01-01 to 2026-12-31 · 7 tables · 102 columns</t>
   </si>
   <si>
     <t>Column</t>
@@ -252,9 +252,15 @@
     <t>age_group</t>
   </si>
   <si>
+    <t>dob</t>
+  </si>
+  <si>
     <t>gender</t>
   </si>
   <si>
+    <t>mobile</t>
+  </si>
+  <si>
     <t>income_segment</t>
   </si>
   <si>
@@ -273,6 +279,9 @@
     <t>acquisition_date</t>
   </si>
   <si>
+    <t>home_store_id</t>
+  </si>
+  <si>
     <t>sku_name</t>
   </si>
   <si>
@@ -570,9 +579,15 @@
     <t>Age cohort.</t>
   </si>
   <si>
+    <t>Date of birth. The customer's age on 2026-01-01 falls inside their age_group (Older_36plus: 36–60).</t>
+  </si>
+  <si>
     <t>Self-reported gender.</t>
   </si>
   <si>
+    <t>Mobile phone number (unique per customer), Thai format 0XX-XXX-XXXX starting 06/08/09. Synthetic.</t>
+  </si>
+  <si>
     <t>Income tier, assigned from the age-group distribution.</t>
   </si>
   <si>
@@ -588,7 +603,10 @@
     <t>Default sweetness pattern; 'adaptive' = no fixed pattern.</t>
   </si>
   <si>
-    <t>Date the customer joined. No order references a customer before this date.</t>
+    <t>Date the customer joined = date of their first purchase. Dates before 2026 are customers who joined in 2025 (pre-existing base); a few sign-ups never buy. No order references a customer before this date.</t>
+  </si>
+  <si>
+    <t>Store where the customer joined and places most (~85%) of their orders; the rest go to a backup store.</t>
   </si>
   <si>
     <t>Unique product identifier. 1–20 = core menu; 21–30 = new items launched during 2026.</t>
@@ -744,7 +762,7 @@
     <t>0</t>
   </si>
   <si>
-    <t>1001</t>
+    <t>1000</t>
   </si>
   <si>
     <t>85.00</t>
@@ -765,7 +783,7 @@
     <t>4.80</t>
   </si>
   <si>
-    <t>39.44</t>
+    <t>37.48</t>
   </si>
   <si>
     <t>3.00</t>
@@ -774,7 +792,10 @@
     <t>85</t>
   </si>
   <si>
-    <t>1000</t>
+    <t>1965-01-11</t>
+  </si>
+  <si>
+    <t>2025-03-01</t>
   </si>
   <si>
     <t>500</t>
@@ -795,9 +816,6 @@
     <t>0.65</t>
   </si>
   <si>
-    <t>2025-03-01</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
@@ -849,7 +867,7 @@
     <t>654.00</t>
   </si>
   <si>
-    <t>123.40</t>
+    <t>122.60</t>
   </si>
   <si>
     <t>30.00</t>
@@ -861,7 +879,7 @@
     <t>56.00</t>
   </si>
   <si>
-    <t>704.00</t>
+    <t>687.00</t>
   </si>
   <si>
     <t>248.08</t>
@@ -876,7 +894,7 @@
     <t>7.20</t>
   </si>
   <si>
-    <t>333.08</t>
+    <t>309.94</t>
   </si>
   <si>
     <t>14.70</t>
@@ -897,7 +915,7 @@
     <t>183</t>
   </si>
   <si>
-    <t>36.60</t>
+    <t>36.40</t>
   </si>
   <si>
     <t>183.00</t>
@@ -906,7 +924,7 @@
     <t>73.20</t>
   </si>
   <si>
-    <t>2026-12-30</t>
+    <t>2008-01-01</t>
   </si>
   <si>
     <t>700</t>
@@ -957,7 +975,7 @@
     <t>direct, YumDash, C2U</t>
   </si>
   <si>
-    <t>ICONSIAMEVE, FLAVOR50, BUILDER3, MALLCOMBO, WELCOME20, MORNING15, HAPPY2FOR1</t>
+    <t>BUILDER3, ICONSIAMEVE, FLAVOR50, MORNING15, HAPPY2FOR1, WELCOME20, MALLCOMBO</t>
   </si>
   <si>
     <t>sunny, cloudy, rainy</t>
@@ -978,6 +996,9 @@
     <t>male, female</t>
   </si>
   <si>
+    <t>e.g. 063-253-1125, 062-838-1255, 092-271-9391</t>
+  </si>
+  <si>
     <t>mid, high, low</t>
   </si>
   <si>
@@ -990,10 +1011,10 @@
     <t>full, less_sweet, adaptive</t>
   </si>
   <si>
-    <t>e.g. Glutinous Green Milk Tea L, Pu'er Milk Tea R, Osmanthus Milk Tea L</t>
-  </si>
-  <si>
-    <t>milk_tea, fruit_tea, blended, pure_tea, cold_brew</t>
+    <t>e.g. Tie Guan Yin Milk Tea R, Jasmine Milk Tea R, Peach Jasmine Tea L</t>
+  </si>
+  <si>
+    <t>milk_tea, fruit_tea, pure_tea, blended, cold_brew</t>
   </si>
   <si>
     <t>e.g. jasmine, glutinous_green, tie_guan_yin</t>
@@ -1005,16 +1026,16 @@
     <t>medium, low, high</t>
   </si>
   <si>
-    <t>PiCha Siam Square, PiCha Park Silom, PiCha ICONSIAM, PiCha Vanit Village, PiCha centralwOrld, PiCha Exchange Tower</t>
-  </si>
-  <si>
-    <t>office, mixed_use, mall, mall_flagship, street</t>
-  </si>
-  <si>
-    <t>Pathum Wan, Khlong Toei, Khlong San, Bang Rak, Ratchathewi</t>
-  </si>
-  <si>
-    <t>power outage, equipment failure, water supply cut, street flooding, building maintenance</t>
+    <t>PiCha Siam Square, PiCha Park Silom, PiCha Vanit Village, PiCha centralwOrld, PiCha Exchange Tower, PiCha ICONSIAM</t>
+  </si>
+  <si>
+    <t>office, mixed_use, mall_flagship, mall, street</t>
+  </si>
+  <si>
+    <t>Pathum Wan, Bang Rak, Ratchathewi, Khlong Toei, Khlong San</t>
+  </si>
+  <si>
+    <t>power outage, water supply cut, equipment failure, street flooding, building maintenance</t>
   </si>
   <si>
     <t>From (child)</t>
@@ -1038,6 +1059,9 @@
     <t>transactions.customer_id</t>
   </si>
   <si>
+    <t>customers.home_store_id</t>
+  </si>
+  <si>
     <t>order_items.transaction_id</t>
   </si>
   <si>
@@ -1182,7 +1206,7 @@
     <t>order_items.net_line_sales_thb = unit_list_price_thb − line_discount_thb</t>
   </si>
   <si>
-    <t>69% of orders have NULL customer_id (anonymous).</t>
+    <t>71% of orders have NULL customer_id (anonymous). About a quarter of customers joined in 2025; new customers join with their first purchase, mostly at busy times, at newly opened stores and after menu drops. Customers buy at their home store and churn after a few months.</t>
   </si>
   <si>
     <t>Core SKUs 1–20 cost 5 THB more from 2026-07-01 (see price_history). Delivery orders carry a 6–18% markup on unit_list_price_thb.</t>
@@ -1712,7 +1736,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -1770,13 +1794,13 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -1788,10 +1812,10 @@
         <v>385595</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1802,10 +1826,10 @@
         <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -1817,10 +1841,10 @@
         <v>380766</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1831,10 +1855,10 @@
         <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1846,10 +1870,10 @@
         <v>365</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1860,10 +1884,10 @@
         <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1875,10 +1899,10 @@
         <v>14</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1889,10 +1913,10 @@
         <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1904,7 +1928,7 @@
         <v>7</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1915,10 +1939,10 @@
         <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1930,10 +1954,10 @@
         <v>7</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1944,10 +1968,10 @@
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1959,10 +1983,10 @@
         <v>12</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1973,13 +1997,13 @@
         <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1991,10 +2015,10 @@
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2005,10 +2029,10 @@
         <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -2020,7 +2044,7 @@
         <v>3</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2031,10 +2055,10 @@
         <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -2046,7 +2070,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2057,28 +2081,28 @@
         <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F12" s="1">
-        <v>264257</v>
+        <v>273430</v>
       </c>
       <c r="G12" s="1">
-        <v>68.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>5366</v>
+        <v>5819</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2089,10 +2113,10 @@
         <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2104,10 +2128,10 @@
         <v>4</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2118,10 +2142,10 @@
         <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2133,10 +2157,10 @@
         <v>555</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2147,10 +2171,10 @@
         <v>46</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2159,13 +2183,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>5691</v>
+        <v>6019</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2176,10 +2200,10 @@
         <v>47</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2191,10 +2215,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2205,10 +2229,10 @@
         <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2220,10 +2244,10 @@
         <v>62</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2234,10 +2258,10 @@
         <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2249,10 +2273,10 @@
         <v>55</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2263,10 +2287,10 @@
         <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2275,13 +2299,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>33199</v>
+        <v>28741</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2292,10 +2316,10 @@
         <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2304,13 +2328,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>19899</v>
+        <v>19927</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2321,10 +2345,10 @@
         <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2336,10 +2360,10 @@
         <v>7</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2350,10 +2374,10 @@
         <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2362,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>10080</v>
+        <v>10141</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2379,10 +2403,10 @@
         <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2394,10 +2418,10 @@
         <v>4</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2408,10 +2432,10 @@
         <v>55</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2420,13 +2444,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>22250</v>
+        <v>21140</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2437,10 +2461,10 @@
         <v>56</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2452,10 +2476,10 @@
         <v>113</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2466,10 +2490,10 @@
         <v>57</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2481,10 +2505,10 @@
         <v>341</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2495,10 +2519,10 @@
         <v>58</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2510,10 +2534,10 @@
         <v>438</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2524,10 +2548,10 @@
         <v>59</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2539,10 +2563,10 @@
         <v>5</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2553,22 +2577,22 @@
         <v>60</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F29" s="1">
-        <v>311249</v>
+        <v>282775</v>
       </c>
       <c r="G29" s="1">
-        <v>80.7</v>
+        <v>73.3</v>
       </c>
       <c r="H29" s="1">
         <v>7</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2579,10 +2603,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2594,7 +2618,7 @@
         <v>3</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2605,10 +2629,10 @@
         <v>62</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2620,7 +2644,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2631,10 +2655,10 @@
         <v>63</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2646,7 +2670,7 @@
         <v>2</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2657,10 +2681,10 @@
         <v>64</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2672,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2683,13 +2707,13 @@
         <v>11</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2701,10 +2725,10 @@
         <v>385595</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2715,13 +2739,13 @@
         <v>65</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2733,10 +2757,10 @@
         <v>4</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2747,13 +2771,13 @@
         <v>14</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2765,10 +2789,10 @@
         <v>30</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2779,10 +2803,10 @@
         <v>66</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2794,10 +2818,10 @@
         <v>1</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2808,10 +2832,10 @@
         <v>67</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2823,10 +2847,10 @@
         <v>95</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2837,10 +2861,10 @@
         <v>68</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2849,13 +2873,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>1794</v>
+        <v>1790</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2866,10 +2890,10 @@
         <v>69</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2878,13 +2902,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>8112</v>
+        <v>6967</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2895,10 +2919,10 @@
         <v>70</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2910,10 +2934,10 @@
         <v>5</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2924,10 +2948,10 @@
         <v>71</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2939,7 +2963,7 @@
         <v>4</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2950,10 +2974,10 @@
         <v>72</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2965,7 +2989,7 @@
         <v>3</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2976,10 +3000,10 @@
         <v>73</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2988,13 +3012,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>3829</v>
+        <v>3275</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3005,10 +3029,10 @@
         <v>36</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3020,10 +3044,10 @@
         <v>380766</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3034,13 +3058,13 @@
         <v>13</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3052,10 +3076,10 @@
         <v>6000</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3066,10 +3090,10 @@
         <v>74</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3081,7 +3105,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -3092,10 +3116,10 @@
         <v>75</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3104,10 +3128,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>2</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>316</v>
+        <v>4275</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -3118,10 +3145,10 @@
         <v>76</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3130,10 +3157,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3144,10 +3171,10 @@
         <v>77</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3156,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>4</v>
+        <v>6000</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3170,10 +3197,10 @@
         <v>78</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3182,10 +3209,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3196,10 +3223,10 @@
         <v>79</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3208,10 +3235,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -3222,10 +3249,10 @@
         <v>80</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3234,10 +3261,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3248,10 +3275,10 @@
         <v>81</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3260,30 +3287,24 @@
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>364</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>293</v>
+        <v>2</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3292,27 +3313,24 @@
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>30</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>288</v>
+        <v>3</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3321,24 +3339,30 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>30</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>321</v>
+        <v>656</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>126</v>
       </c>
+      <c r="D57" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="E57" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3347,10 +3371,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>5</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>322</v>
+        <v>6</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -3358,13 +3385,16 @@
         <v>7</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>126</v>
       </c>
+      <c r="D58" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="E58" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3373,10 +3403,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>15</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>323</v>
+        <v>30</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -3387,10 +3420,10 @@
         <v>85</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3399,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3413,10 +3446,10 @@
         <v>86</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3425,10 +3458,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -3439,10 +3472,10 @@
         <v>87</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3451,10 +3484,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -3465,10 +3498,10 @@
         <v>88</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3480,7 +3513,7 @@
         <v>2</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3494,7 +3527,7 @@
         <v>126</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3506,7 +3539,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3517,10 +3550,10 @@
         <v>90</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3531,11 +3564,8 @@
       <c r="H64" s="1">
         <v>2</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>294</v>
+      <c r="K64" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3546,10 +3576,10 @@
         <v>91</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3558,13 +3588,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>12</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>295</v>
+        <v>2</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3575,10 +3602,10 @@
         <v>92</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3587,13 +3614,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="1">
-        <v>1</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>238</v>
+        <v>2</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3604,10 +3628,10 @@
         <v>93</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3616,13 +3640,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>251</v>
+        <v>300</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3636,7 +3660,7 @@
         <v>126</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3645,10 +3669,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="1">
-        <v>3</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>325</v>
+        <v>12</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3659,10 +3686,10 @@
         <v>95</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3671,10 +3698,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>2</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>312</v>
+        <v>1</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3685,10 +3715,10 @@
         <v>96</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3697,10 +3727,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>2</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>312</v>
+        <v>1</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3711,10 +3744,10 @@
         <v>97</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3723,10 +3756,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3737,10 +3770,10 @@
         <v>98</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3749,30 +3782,24 @@
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>7</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>296</v>
+        <v>2</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -3781,27 +3808,24 @@
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>6</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>252</v>
+        <v>2</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>126</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -3810,24 +3834,24 @@
         <v>0</v>
       </c>
       <c r="H74" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -3836,10 +3860,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="1">
-        <v>5</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>327</v>
+        <v>7</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3847,13 +3874,16 @@
         <v>8</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>126</v>
       </c>
+      <c r="D76" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="E76" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -3862,10 +3892,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>5</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>328</v>
+        <v>6</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3876,10 +3909,10 @@
         <v>102</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -3890,11 +3923,8 @@
       <c r="H77" s="1">
         <v>6</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>297</v>
+      <c r="K77" s="1" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -3905,10 +3935,10 @@
         <v>103</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -3917,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3931,10 +3961,10 @@
         <v>104</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -3945,11 +3975,8 @@
       <c r="H79" s="1">
         <v>5</v>
       </c>
-      <c r="I79" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>298</v>
+      <c r="K79" s="1" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -3960,10 +3987,10 @@
         <v>105</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -3975,10 +4002,10 @@
         <v>6</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3989,10 +4016,10 @@
         <v>106</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4001,13 +4028,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>5</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>298</v>
+        <v>2</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -4018,10 +4042,10 @@
         <v>107</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -4030,13 +4054,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -4047,10 +4071,10 @@
         <v>108</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -4059,10 +4083,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="1">
-        <v>2</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>312</v>
+        <v>6</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -4073,10 +4100,10 @@
         <v>109</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -4085,13 +4112,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>251</v>
+        <v>304</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -4102,10 +4129,10 @@
         <v>110</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -4117,10 +4144,10 @@
         <v>6</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4131,10 +4158,10 @@
         <v>111</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -4143,13 +4170,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="1">
-        <v>5</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>271</v>
+        <v>2</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -4160,10 +4184,10 @@
         <v>112</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -4172,13 +4196,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>302</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -4189,10 +4213,10 @@
         <v>113</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -4204,10 +4228,10 @@
         <v>6</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -4218,10 +4242,10 @@
         <v>114</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -4230,13 +4254,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -4247,10 +4271,10 @@
         <v>115</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -4259,13 +4283,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>259</v>
+        <v>308</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -4276,10 +4300,10 @@
         <v>116</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -4291,10 +4315,10 @@
         <v>6</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>245</v>
+        <v>309</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -4305,10 +4329,10 @@
         <v>117</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -4317,10 +4341,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="1">
-        <v>2</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>312</v>
+        <v>6</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -4331,10 +4358,10 @@
         <v>118</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -4343,30 +4370,27 @@
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>304</v>
+        <v>265</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -4375,27 +4399,27 @@
         <v>0</v>
       </c>
       <c r="H94" s="1">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>288</v>
+        <v>251</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -4404,30 +4428,24 @@
         <v>0</v>
       </c>
       <c r="H95" s="1">
-        <v>14</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>305</v>
+        <v>2</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D96" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -4436,13 +4454,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -4450,45 +4468,45 @@
         <v>9</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F97" s="1">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1">
         <v>30</v>
       </c>
-      <c r="G97" s="1">
-        <v>60</v>
-      </c>
-      <c r="H97" s="1">
-        <v>1</v>
-      </c>
       <c r="I97" s="1" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -4497,30 +4515,30 @@
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -4529,50 +4547,143 @@
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F100" s="1">
+        <v>30</v>
+      </c>
+      <c r="G100" s="1">
+        <v>60</v>
+      </c>
+      <c r="H100" s="1">
+        <v>1</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C100" s="1" t="s">
+      <c r="B101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F100" s="1">
-        <v>0</v>
-      </c>
-      <c r="G100" s="1">
-        <v>0</v>
-      </c>
-      <c r="H100" s="1">
+      <c r="D101" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F101" s="1">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0</v>
+      </c>
+      <c r="H101" s="1">
+        <v>6</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F102" s="1">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0</v>
+      </c>
+      <c r="H102" s="1">
+        <v>14</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F103" s="1">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1">
         <v>5</v>
       </c>
-      <c r="K100" s="1" t="s">
-        <v>329</v>
+      <c r="K103" s="1" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K100"/>
+  <autoFilter ref="A1:K103"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="1" customWidth="1"/>
@@ -4584,30 +4695,30 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -4615,16 +4726,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -4632,13 +4743,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -4646,13 +4757,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -4660,13 +4771,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -4674,20 +4785,34 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E7"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4708,177 +4833,177 @@
         <v>27</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D2" s="1">
-        <v>1840</v>
+        <v>12305</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D3" s="1">
-        <v>1395</v>
+        <v>9394</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D4" s="1">
-        <v>15967</v>
+        <v>26970</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D5" s="1">
-        <v>16436</v>
+        <v>12943</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="D6" s="1">
-        <v>3300</v>
+        <v>8533</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="D7" s="1">
-        <v>9120</v>
+        <v>7727</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D8" s="1">
-        <v>26288</v>
+        <v>24948</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B13" s="1">
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B14" s="1">
         <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4898,90 +5023,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/picha12mo/data_dict_en.xlsx
+++ b/picha12mo/data_dict_en.xlsx
@@ -15,17 +15,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Codes!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$K$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Notes!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Overview!$A$3:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Relationships!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$K$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Notes!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Overview!$A$3:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Relationships!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="458">
   <si>
     <t>Table</t>
   </si>
@@ -60,6 +60,12 @@
     <t>store_closures</t>
   </si>
   <si>
+    <t>delivery_prices</t>
+  </si>
+  <si>
+    <t>stockouts</t>
+  </si>
+  <si>
     <t>transaction_id</t>
   </si>
   <si>
@@ -81,10 +87,16 @@
     <t>(store_id, date)</t>
   </si>
   <si>
+    <t>(store_id, platform, sku_id, valid_from)</t>
+  </si>
+  <si>
+    <t>(store_id, date, sku_id)</t>
+  </si>
+  <si>
     <t>One row per order (order header) with channel, customer, financial and operational metrics.</t>
   </si>
   <si>
-    <t>One row per drink in an order. qty is always 1; basket size is the number of lines.</t>
+    <t>One row per drink and set of options in an order; repeated identical cups share one line with qty &gt; 1.</t>
   </si>
   <si>
     <t>Registered customer profiles. Orders without a customer_id are anonymous.</t>
@@ -102,10 +114,16 @@
     <t>Days a store was closed and sold nothing (planned maintenance or unplanned incidents).</t>
   </si>
   <si>
+    <t>Delivery-app menu price per store, platform and SKU over time. Fixed for each validity period; changes only when the in-store price changes.</t>
+  </si>
+  <si>
+    <t>Store-days when a limited item (seasonal_flag = 1) sold out. Later cups that day switched to a same-family drink, so recorded sales of the item are capped (censored demand).</t>
+  </si>
+  <si>
     <t>PiCha Tea House — Data Dictionary (picha12mo.duckdb)</t>
   </si>
   <si>
-    <t>2026-01-01 to 2026-12-31 · 7 tables · 102 columns</t>
+    <t>2026-01-01 to 2026-12-31 · 9 tables · 123 columns</t>
   </si>
   <si>
     <t>Column</t>
@@ -159,6 +177,15 @@
     <t>platform</t>
   </si>
   <si>
+    <t>payment_method</t>
+  </si>
+  <si>
+    <t>order_status</t>
+  </si>
+  <si>
+    <t>status_reason</t>
+  </si>
+  <si>
     <t>basket_qty</t>
   </si>
   <si>
@@ -180,6 +207,9 @@
     <t>net_sales_thb</t>
   </si>
   <si>
+    <t>refund_thb</t>
+  </si>
+  <si>
     <t>cogs_thb</t>
   </si>
   <si>
@@ -246,6 +276,9 @@
     <t>add_on</t>
   </si>
   <si>
+    <t>add_on_price_thb</t>
+  </si>
+  <si>
     <t>line_cogs_thb</t>
   </si>
   <si>
@@ -279,9 +312,18 @@
     <t>acquisition_date</t>
   </si>
   <si>
+    <t>preferred_channel</t>
+  </si>
+  <si>
+    <t>preferred_daypart</t>
+  </si>
+  <si>
     <t>home_store_id</t>
   </si>
   <si>
+    <t>acquisition_campaign</t>
+  </si>
+  <si>
     <t>sku_name</t>
   </si>
   <si>
@@ -405,6 +447,21 @@
     <t>reason</t>
   </si>
   <si>
+    <t>app_price_thb</t>
+  </si>
+  <si>
+    <t>markup</t>
+  </si>
+  <si>
+    <t>units_prepared</t>
+  </si>
+  <si>
+    <t>sold_out_at</t>
+  </si>
+  <si>
+    <t>cups_switched</t>
+  </si>
+  <si>
     <t>BIGINT</t>
   </si>
   <si>
@@ -471,13 +528,22 @@
     <t>Delivery platform; 'direct' for dine-in and to-go.</t>
   </si>
   <si>
+    <t>How the order was paid. Delivery orders = 'platform'. In store: PromptPay QR is most common; cash skews older, cards skew high-income and tourist stores (ICONSIAM, Siam Square), TrueMoney skews Gen Z. Registered customers mostly use their usual method.</t>
+  </si>
+  <si>
     <t>Registered customer; NULL = anonymous order.</t>
   </si>
   <si>
-    <t>Number of drinks in the order.</t>
-  </si>
-  <si>
-    <t>Sum of unit_list_price_thb over the order's lines, before discounts (THB).</t>
+    <t>completed, cancelled or refunded. Cancelled orders keep the ordered amounts but earn no revenue.</t>
+  </si>
+  <si>
+    <t>Why the order was cancelled (no_rider, customer_cancelled, walked_out) or refunded (missing_item, wrong_item, spilled); NULL = completed.</t>
+  </si>
+  <si>
+    <t>Number of cups in the order (sum of order_items.qty). Office lunch group orders run 5–12 cups.</t>
+  </si>
+  <si>
+    <t>Sum of unit_list_price_thb + add_on_price_thb over the order's lines, before discounts (THB).</t>
   </si>
   <si>
     <t>Sum of line_discount_thb (THB).</t>
@@ -492,7 +558,10 @@
     <t>Delivery platform subsidy toward the fee (THB).</t>
   </si>
   <si>
-    <t>gross_sales_thb − item_discount_thb − order_discount_thb + delivery_fee_paid_by_customer.</t>
+    <t>gross_sales_thb − item_discount_thb − order_discount_thb + delivery_fee_paid_by_customer (as ordered; see order_status and refund_thb).</t>
+  </si>
+  <si>
+    <t>Amount refunded (THB): one cup for missing/wrong items, the whole order for spills; 0 otherwise.</t>
   </si>
   <si>
     <t>Sum of line_cogs_thb (THB).</t>
@@ -510,22 +579,22 @@
     <t>net_sales_thb − cogs_thb − packaging_cost_thb − labor_alloc_thb − platform_commission_thb.</t>
   </si>
   <si>
-    <t>Preparation time (minutes), scaled by how busy the store is that day.</t>
-  </si>
-  <si>
-    <t>Customer wait time for dine-in / to-go (minutes); 0 for delivery.</t>
-  </si>
-  <si>
-    <t>Rider pickup time for delivery (minutes); 0 otherwise.</t>
-  </si>
-  <si>
-    <t>Customer satisfaction, 1 (worst) – 5 (best).</t>
+    <t>Preparation time (minutes) for the order: base + per item + delivery packing.</t>
+  </si>
+  <si>
+    <t>Customer wait time for dine-in / to-go (minutes); grows with the queue in that store-hour. 0 for delivery.</t>
+  </si>
+  <si>
+    <t>Rider pickup time for delivery (minutes): queue + rider wait, longer in rain and at peak hours. 0 otherwise.</t>
+  </si>
+  <si>
+    <t>Customer satisfaction, 1 (worst) – 5 (best). Cancelled and refunded orders are rated 1–2.</t>
   </si>
   <si>
     <t>Promotional campaign code applied to the order; NULL = none.</t>
   </si>
   <si>
-    <t>Weather on the order date. Rain lowers walk-in demand and raises delivery share.</t>
+    <t>Weather at the hour of the order. On rainy days rain falls in a window of 1–4 hours (mostly 14:00–18:00); other hours of the day are 'cloudy'. Rain raises delivery share, rider delays and cancellations.</t>
   </si>
   <si>
     <t>1 = peak hours (11–13, 17–19).</t>
@@ -546,19 +615,19 @@
     <t>Product ordered.</t>
   </si>
   <si>
-    <t>Quantity per line (always 1).</t>
-  </si>
-  <si>
-    <t>Unit price (THB) on the order date, including the July price increase and any delivery markup.</t>
-  </si>
-  <si>
-    <t>Discount on this line (THB): loyalty perk, time-based promo or campaign.</t>
-  </si>
-  <si>
-    <t>unit_list_price_thb − line_discount_thb.</t>
-  </si>
-  <si>
-    <t>Selected sweetness (0 = no sugar, 100 = full).</t>
+    <t>Cups on this line (identical drink and options). Group orders often repeat the same drink.</t>
+  </si>
+  <si>
+    <t>Drink price per cup (THB) on the order date, including the July price increase. Delivery lines use the fixed app price (see delivery_prices).</t>
+  </si>
+  <si>
+    <t>Total discount on the line's drinks (THB): loyalty perk, time-based promo or campaign. Add-ons are never discounted.</t>
+  </si>
+  <si>
+    <t>qty × (unit_list_price_thb + add_on_price_thb) − line_discount_thb.</t>
+  </si>
+  <si>
+    <t>Selected sweetness (0 = no sugar, 100 = full). Depends on the customer's preference, health focus and age, and on the drink: pure tea and cold brew are usually 0–30%.</t>
   </si>
   <si>
     <t>Ice preference.</t>
@@ -567,7 +636,10 @@
     <t>Topping add-on.</t>
   </si>
   <si>
-    <t>Cost of goods sold for the line (THB): 32% of net for milk tea, 40% for Fresh Orange Jasmine, 28% otherwise.</t>
+    <t>Add-on price per cup (THB): extra_pearl 10, extra_milk_foam 15, none 0.</t>
+  </si>
+  <si>
+    <t>Ingredient cost of the whole line (THB), per cup: per-cup cost by family and size (+4% from 2026-07-01) plus add-on cost (pearl 3, foam 5). Does not change with discounts.</t>
   </si>
   <si>
     <t>Timestamp of the parent order.</t>
@@ -591,7 +663,7 @@
     <t>Income tier, assigned from the age-group distribution.</t>
   </si>
   <si>
-    <t>Loyalty tier at the start of the simulation (tiers evolve weekly via a Markov chain; see loyalty_summary.csv).</t>
+    <t>Loyalty tier in the first week of 2026. Tiers follow rolling 13-week menu-price spend (silver ≥ 1,200 THB, gold ≥ 3,000 THB); upgrades apply at once, downgrades at quarter starts; 'none' = not enrolled. Weekly history in loyalty_summary.csv.</t>
   </si>
   <si>
     <t>How the customer first discovered PiCha.</t>
@@ -606,9 +678,18 @@
     <t>Date the customer joined = date of their first purchase. Dates before 2026 are customers who joined in 2025 (pre-existing base); a few sign-ups never buy. No order references a customer before this date.</t>
   </si>
   <si>
+    <t>The customer's usual channel; 60–90% of their orders follow their routine (usual channel and daypart).</t>
+  </si>
+  <si>
+    <t>The customer's usual time of day: morning 9–10, lunch 11–13, afternoon 14–16, evening 17–19, late 20–22.</t>
+  </si>
+  <si>
     <t>Store where the customer joined and places most (~85%) of their orders; the rest go to a backup store.</t>
   </si>
   <si>
+    <t>Sign-up campaign the customer joined in (NULL = joined outside a campaign). Campaign joiners stay for a shorter time and redeem more perks.</t>
+  </si>
+  <si>
     <t>Unique product identifier. 1–20 = core menu; 21–30 = new items launched during 2026.</t>
   </si>
   <si>
@@ -705,10 +786,10 @@
     <t>Total staff.</t>
   </si>
   <si>
-    <t>Number of baristas (affects prep-time scaling).</t>
-  </si>
-  <si>
-    <t>Maximum orders per day (affects wait-time scaling).</t>
+    <t>Number of baristas (sets hourly queue capacity: 70% on shift × 30 cups per barista-hour).</t>
+  </si>
+  <si>
+    <t>Maximum orders per day (affects prep-time scaling).</t>
   </si>
   <si>
     <t>Distance to nearest BTS Skytrain station (meters).</t>
@@ -747,10 +828,43 @@
     <t>Reason for closure.</t>
   </si>
   <si>
+    <t>Store.</t>
+  </si>
+  <si>
+    <t>Delivery platform.</t>
+  </si>
+  <si>
+    <t>Price shown in the delivery app (THB): in-store price × markup, rounded to the nearest price ending in 9.</t>
+  </si>
+  <si>
+    <t>Store × platform × SKU markup over the in-store price (branch range 1.06–1.18).</t>
+  </si>
+  <si>
+    <t>First date this app price applies.</t>
+  </si>
+  <si>
+    <t>Last date this app price applies; NULL = current price.</t>
+  </si>
+  <si>
+    <t>Day the item sold out.</t>
+  </si>
+  <si>
+    <t>Item that sold out.</t>
+  </si>
+  <si>
+    <t>Cups the store prepped for the day (about 1.15 × its average daily sales of the item, ± 15%).</t>
+  </si>
+  <si>
+    <t>Time the last prepped cup was sold.</t>
+  </si>
+  <si>
+    <t>Cups ordered after the sell-out that switched to another drink of the same family.</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>2026-01-01 09:00:57</t>
+    <t>2026-01-01 09:05:58</t>
   </si>
   <si>
     <t>2026-01-01</t>
@@ -774,7 +888,7 @@
     <t>68.00</t>
   </si>
   <si>
-    <t>19.04</t>
+    <t>24.00</t>
   </si>
   <si>
     <t>2.00</t>
@@ -783,7 +897,7 @@
     <t>4.80</t>
   </si>
   <si>
-    <t>37.48</t>
+    <t>29.20</t>
   </si>
   <si>
     <t>3.00</t>
@@ -846,6 +960,18 @@
     <t>2026-01-29</t>
   </si>
   <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>1.06</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>2026-01-01 15:46:32</t>
+  </si>
+  <si>
     <t>385,595</t>
   </si>
   <si>
@@ -864,10 +990,10 @@
     <t>6999</t>
   </si>
   <si>
-    <t>654.00</t>
-  </si>
-  <si>
-    <t>122.60</t>
+    <t>1,758.00</t>
+  </si>
+  <si>
+    <t>329.60</t>
   </si>
   <si>
     <t>30.00</t>
@@ -879,49 +1005,58 @@
     <t>56.00</t>
   </si>
   <si>
-    <t>687.00</t>
-  </si>
-  <si>
-    <t>248.08</t>
-  </si>
-  <si>
-    <t>20.00</t>
-  </si>
-  <si>
-    <t>149.73</t>
-  </si>
-  <si>
-    <t>7.20</t>
-  </si>
-  <si>
-    <t>309.94</t>
-  </si>
-  <si>
-    <t>14.70</t>
-  </si>
-  <si>
-    <t>37.20</t>
-  </si>
-  <si>
-    <t>58.20</t>
+    <t>1,758.56</t>
+  </si>
+  <si>
+    <t>1,247.91</t>
+  </si>
+  <si>
+    <t>586.32</t>
+  </si>
+  <si>
+    <t>60.00</t>
+  </si>
+  <si>
+    <t>399.87</t>
+  </si>
+  <si>
+    <t>13.60</t>
+  </si>
+  <si>
+    <t>1,043.94</t>
+  </si>
+  <si>
+    <t>25.30</t>
+  </si>
+  <si>
+    <t>96.90</t>
+  </si>
+  <si>
+    <t>215.80</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>36.40</t>
-  </si>
-  <si>
-    <t>183.00</t>
-  </si>
-  <si>
-    <t>73.20</t>
+    <t>179</t>
+  </si>
+  <si>
+    <t>189.00</t>
+  </si>
+  <si>
+    <t>1,318.76</t>
+  </si>
+  <si>
+    <t>15.00</t>
+  </si>
+  <si>
+    <t>369.00</t>
   </si>
   <si>
     <t>2008-01-01</t>
@@ -966,6 +1101,15 @@
     <t>2026-12-17</t>
   </si>
   <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>2026-12-31 20:31:02</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
     <t>Saturday, Sunday, Friday, Thursday, Wednesday, Tuesday, Monday</t>
   </si>
   <si>
@@ -975,7 +1119,16 @@
     <t>direct, YumDash, C2U</t>
   </si>
   <si>
-    <t>BUILDER3, ICONSIAMEVE, FLAVOR50, MORNING15, HAPPY2FOR1, WELCOME20, MALLCOMBO</t>
+    <t>platform, promptpay_qr, credit_card, cash, truemoney</t>
+  </si>
+  <si>
+    <t>completed, cancelled, refunded</t>
+  </si>
+  <si>
+    <t>no_rider, walked_out, missing_item, wrong_item, customer_cancelled, spilled</t>
+  </si>
+  <si>
+    <t>ICONSIAMEVE, BUILDER3, MORNING15, FLAVOR50, HAPPY2FOR1, MALLCOMBO, WELCOME20</t>
   </si>
   <si>
     <t>sunny, cloudy, rainy</t>
@@ -996,13 +1149,13 @@
     <t>male, female</t>
   </si>
   <si>
-    <t>e.g. 063-253-1125, 062-838-1255, 092-271-9391</t>
+    <t>e.g. 095-109-0834, 065-503-6689, 095-739-2989</t>
   </si>
   <si>
     <t>mid, high, low</t>
   </si>
   <si>
-    <t>member, silver, none, gold</t>
+    <t>member, none, gold, silver</t>
   </si>
   <si>
     <t>tiktok, instagram, word_of_mouth, delivery_app, walk_in</t>
@@ -1011,10 +1164,16 @@
     <t>full, less_sweet, adaptive</t>
   </si>
   <si>
-    <t>e.g. Tie Guan Yin Milk Tea R, Jasmine Milk Tea R, Peach Jasmine Tea L</t>
-  </si>
-  <si>
-    <t>milk_tea, fruit_tea, pure_tea, blended, cold_brew</t>
+    <t>lunch, evening, afternoon, late, morning</t>
+  </si>
+  <si>
+    <t>Year-end festive, CNY viral campaign, Songkran campaign</t>
+  </si>
+  <si>
+    <t>e.g. Glutinous Green Milk Tea R, Fresh Orange Jasmine Tea L, Thai Tea Frappe L</t>
+  </si>
+  <si>
+    <t>milk_tea, fruit_tea, blended, pure_tea, cold_brew</t>
   </si>
   <si>
     <t>e.g. jasmine, glutinous_green, tie_guan_yin</t>
@@ -1026,16 +1185,19 @@
     <t>medium, low, high</t>
   </si>
   <si>
-    <t>PiCha Siam Square, PiCha Park Silom, PiCha Vanit Village, PiCha centralwOrld, PiCha Exchange Tower, PiCha ICONSIAM</t>
-  </si>
-  <si>
-    <t>office, mixed_use, mall_flagship, mall, street</t>
-  </si>
-  <si>
-    <t>Pathum Wan, Bang Rak, Ratchathewi, Khlong Toei, Khlong San</t>
-  </si>
-  <si>
-    <t>power outage, water supply cut, equipment failure, street flooding, building maintenance</t>
+    <t>PiCha Siam Square, PiCha Park Silom, PiCha centralwOrld, PiCha Exchange Tower, PiCha Vanit Village, PiCha ICONSIAM</t>
+  </si>
+  <si>
+    <t>office, street, mall_flagship, mixed_use, mall</t>
+  </si>
+  <si>
+    <t>Pathum Wan, Khlong Toei, Khlong San, Ratchathewi, Bang Rak</t>
+  </si>
+  <si>
+    <t>power outage, equipment failure, water supply cut, building maintenance, street flooding</t>
+  </si>
+  <si>
+    <t>YumDash, C2U</t>
   </si>
   <si>
     <t>From (child)</t>
@@ -1074,6 +1236,18 @@
     <t>store_closures.store_id</t>
   </si>
   <si>
+    <t>delivery_prices.store_id</t>
+  </si>
+  <si>
+    <t>delivery_prices.sku_id</t>
+  </si>
+  <si>
+    <t>stockouts.store_id</t>
+  </si>
+  <si>
+    <t>stockouts.sku_id</t>
+  </si>
+  <si>
     <t>stores.store_id</t>
   </si>
   <si>
@@ -1203,13 +1377,16 @@
     <t>contribution_margin_thb = net_sales_thb − cogs_thb − packaging_cost_thb − labor_alloc_thb − platform_commission_thb</t>
   </si>
   <si>
-    <t>order_items.net_line_sales_thb = unit_list_price_thb − line_discount_thb</t>
-  </si>
-  <si>
-    <t>71% of orders have NULL customer_id (anonymous). About a quarter of customers joined in 2025; new customers join with their first purchase, mostly at busy times, at newly opened stores and after menu drops. Customers buy at their home store and churn after a few months.</t>
-  </si>
-  <si>
-    <t>Core SKUs 1–20 cost 5 THB more from 2026-07-01 (see price_history). Delivery orders carry a 6–18% markup on unit_list_price_thb.</t>
+    <t>order_items.net_line_sales_thb = qty × (unit_list_price_thb + add_on_price_thb) − line_discount_thb</t>
+  </si>
+  <si>
+    <t>Recognised net sales = net_sales_thb − refund_thb for completed/refunded orders; 0 for cancelled orders. The pro forma uses this; no_rider cancellations still carry COGS and packaging (drinks were made).</t>
+  </si>
+  <si>
+    <t>77% of orders have NULL customer_id (anonymous). About a quarter of customers joined in 2025; new customers join with their first purchase, mostly at busy times, at newly opened stores and after menu drops. Customers buy at their home store, mostly through their preferred channel and daypart, and churn after a few months — sooner if they joined in a campaign, and some leave for good after an order with a long wait.</t>
+  </si>
+  <si>
+    <t>Core SKUs 1–20 cost 5 THB more from 2026-07-01 (see price_history). Delivery orders use a fixed app price per store × platform × SKU (see delivery_prices), 6–18% above the in-store price. Ingredient costs rose 4% on the same date.</t>
   </si>
   <si>
     <t>New items launch on the 1st of Feb, Apr, Jun, Aug, Oct and Dec; seasonal_flag = 1 items are limited-time and stop selling at their end date. SKUs 9–10 are discontinued from 2026-03-01 and SKU 7 from 2026-08-01.</t>
@@ -1597,7 +1774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="1" customWidth="1"/>
@@ -1608,12 +1785,12 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1638,10 +1815,10 @@
         <v>385595</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1649,13 +1826,13 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>658717</v>
+        <v>601206</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1666,10 +1843,10 @@
         <v>6000</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1680,10 +1857,10 @@
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1694,10 +1871,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1708,10 +1885,10 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1722,21 +1899,49 @@
         <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>600</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1283</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D10"/>
+  <autoFilter ref="A3:D12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -1756,34 +1961,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1791,16 +1996,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -1812,10 +2017,10 @@
         <v>385595</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>273</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1823,13 +2028,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -1838,13 +2043,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>380766</v>
+        <v>380378</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1852,13 +2057,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1870,10 +2075,10 @@
         <v>365</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>275</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1881,13 +2086,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1899,10 +2104,10 @@
         <v>14</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1910,13 +2115,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1928,7 +2133,7 @@
         <v>7</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1936,13 +2141,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1954,10 +2159,10 @@
         <v>7</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1965,13 +2170,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1983,10 +2188,10 @@
         <v>12</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1994,16 +2199,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -2015,10 +2220,10 @@
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2026,13 +2231,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -2044,7 +2249,7 @@
         <v>3</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2052,13 +2257,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -2070,7 +2275,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2078,31 +2283,25 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="F12" s="1">
-        <v>273430</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>70.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>5819</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>278</v>
+        <v>5</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2110,28 +2309,31 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>298239</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="H13" s="1">
-        <v>4</v>
+        <v>5811</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>240</v>
+        <v>283</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>265</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2139,13 +2341,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2154,13 +2356,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>555</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>279</v>
+        <v>3</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2168,28 +2367,25 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>378628</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="H15" s="1">
-        <v>6019</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>280</v>
+        <v>6</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2197,13 +2393,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2212,27 +2408,27 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2241,27 +2437,27 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>62</v>
+        <v>872</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2270,27 +2466,27 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>55</v>
+        <v>5419</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2299,27 +2495,27 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>28741</v>
+        <v>2</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2328,27 +2524,27 @@
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>19927</v>
+        <v>62</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2357,27 +2553,27 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2386,27 +2582,27 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>10141</v>
+        <v>28718</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2415,27 +2611,27 @@
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>4</v>
+        <v>946</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2444,27 +2640,27 @@
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>21140</v>
+        <v>2112</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2473,27 +2669,27 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2502,27 +2698,27 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>341</v>
+        <v>9859</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2531,27 +2727,27 @@
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>438</v>
+        <v>12</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2560,53 +2756,56 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>5</v>
+        <v>26257</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="F29" s="1">
-        <v>282775</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>73.3</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>7</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>217</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2615,24 +2814,27 @@
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>3</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>837</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2641,24 +2843,27 @@
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>2</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>886</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2667,10 +2872,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>2</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>318</v>
+        <v>5</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2678,42 +2886,39 @@
         <v>4</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>285730</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2722,30 +2927,24 @@
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>385595</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>273</v>
+        <v>3</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2754,30 +2953,24 @@
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>4</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>265</v>
+        <v>2</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2786,27 +2979,24 @@
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>30</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>294</v>
+        <v>2</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2815,13 +3005,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>1</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>240</v>
+        <v>2</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2829,13 +3016,16 @@
         <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2844,13 +3034,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>95</v>
+        <v>385595</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2858,13 +3048,16 @@
         <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2873,13 +3066,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>1790</v>
+        <v>11</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2887,13 +3080,16 @@
         <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2902,13 +3098,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>6967</v>
+        <v>30</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>297</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2916,13 +3112,13 @@
         <v>5</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2931,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>258</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2945,13 +3141,13 @@
         <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2960,10 +3156,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>4</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>319</v>
+        <v>23</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2971,13 +3170,13 @@
         <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2986,10 +3185,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>3</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>320</v>
+        <v>2318</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2997,13 +3199,13 @@
         <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3012,13 +3214,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>3275</v>
+        <v>12333</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>298</v>
+        <v>341</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3026,13 +3228,13 @@
         <v>5</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3041,30 +3243,27 @@
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>380766</v>
+        <v>5</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3073,27 +3272,24 @@
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>278</v>
+        <v>4</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3102,24 +3298,24 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>321</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3128,27 +3324,27 @@
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>4275</v>
+        <v>3</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>299</v>
+        <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3157,24 +3353,27 @@
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>2</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>322</v>
+        <v>180</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3183,10 +3382,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>6000</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>323</v>
+        <v>380378</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3194,13 +3396,16 @@
         <v>6</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3209,10 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>3</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>324</v>
+        <v>6000</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3220,13 +3428,13 @@
         <v>6</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3238,7 +3446,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>325</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -3246,13 +3454,13 @@
         <v>6</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3261,10 +3469,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>5</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>326</v>
+        <v>4275</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3272,13 +3483,13 @@
         <v>6</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3290,7 +3501,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -3298,13 +3509,13 @@
         <v>6</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3313,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>3</v>
+        <v>6000</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>327</v>
+        <v>374</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -3324,13 +3535,13 @@
         <v>6</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3339,13 +3550,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>656</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>275</v>
+        <v>3</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -3353,16 +3561,13 @@
         <v>6</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3371,30 +3576,24 @@
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>6</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>259</v>
+        <v>4</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3403,27 +3602,24 @@
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>30</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3432,24 +3628,24 @@
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3458,24 +3654,24 @@
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>329</v>
+        <v>378</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3484,24 +3680,27 @@
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>15</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>330</v>
+        <v>656</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3510,24 +3709,24 @@
         <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>318</v>
+        <v>362</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3536,24 +3735,27 @@
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3562,36 +3764,39 @@
         <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>2</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>318</v>
+        <v>6</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="F65" s="1">
-        <v>0</v>
+        <v>5068</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>84.5</v>
       </c>
       <c r="H65" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>318</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3599,13 +3804,16 @@
         <v>7</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3614,10 +3822,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="1">
-        <v>2</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>331</v>
+        <v>30</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3625,13 +3836,13 @@
         <v>7</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3640,13 +3851,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>2</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>300</v>
+        <v>30</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3654,13 +3862,13 @@
         <v>7</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3669,13 +3877,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="1">
-        <v>12</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>301</v>
+        <v>5</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3683,13 +3888,13 @@
         <v>7</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3698,13 +3903,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>1</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>244</v>
+        <v>15</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3712,13 +3914,13 @@
         <v>7</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3727,13 +3929,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>1</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>258</v>
+        <v>2</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3741,13 +3940,13 @@
         <v>7</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3756,10 +3955,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3767,13 +3966,13 @@
         <v>7</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3785,7 +3984,7 @@
         <v>2</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>318</v>
+        <v>369</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3793,13 +3992,13 @@
         <v>7</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -3811,7 +4010,7 @@
         <v>2</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>318</v>
+        <v>369</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3819,13 +4018,13 @@
         <v>7</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -3837,7 +4036,7 @@
         <v>2</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>318</v>
+        <v>384</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3845,13 +4044,13 @@
         <v>7</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -3860,30 +4059,27 @@
         <v>0</v>
       </c>
       <c r="H75" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>242</v>
+        <v>295</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>302</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -3892,27 +4088,27 @@
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>259</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -3921,24 +4117,27 @@
         <v>0</v>
       </c>
       <c r="H77" s="1">
-        <v>6</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>333</v>
+        <v>1</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -3947,24 +4146,27 @@
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>5</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>334</v>
+        <v>1</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -3973,24 +4175,24 @@
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -3999,27 +4201,24 @@
         <v>0</v>
       </c>
       <c r="H80" s="1">
-        <v>6</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>303</v>
+        <v>2</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4031,21 +4230,21 @@
         <v>2</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>318</v>
+        <v>369</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -4054,27 +4253,24 @@
         <v>0</v>
       </c>
       <c r="H82" s="1">
-        <v>5</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>304</v>
+        <v>2</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -4083,13 +4279,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>305</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -4097,13 +4293,16 @@
         <v>8</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -4112,13 +4311,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -4126,13 +4325,13 @@
         <v>8</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -4143,11 +4342,8 @@
       <c r="H85" s="1">
         <v>6</v>
       </c>
-      <c r="I85" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>306</v>
+      <c r="K85" s="1" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4155,13 +4351,13 @@
         <v>8</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -4170,10 +4366,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -4181,13 +4377,13 @@
         <v>8</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -4196,13 +4392,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>6</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>258</v>
+        <v>5</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -4210,13 +4403,13 @@
         <v>8</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -4228,10 +4421,10 @@
         <v>6</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -4239,13 +4432,13 @@
         <v>8</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -4254,13 +4447,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="1">
-        <v>5</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>277</v>
+        <v>2</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -4268,13 +4458,13 @@
         <v>8</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -4283,13 +4473,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -4297,13 +4487,13 @@
         <v>8</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -4315,10 +4505,10 @@
         <v>6</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -4326,13 +4516,13 @@
         <v>8</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -4341,13 +4531,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>257</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -4355,13 +4545,13 @@
         <v>8</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -4370,13 +4560,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>265</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -4384,13 +4574,13 @@
         <v>8</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -4399,13 +4589,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="1">
-        <v>6</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>251</v>
+        <v>2</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -4413,13 +4600,13 @@
         <v>8</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -4428,10 +4615,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="1">
-        <v>2</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>318</v>
+        <v>6</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -4439,13 +4629,13 @@
         <v>8</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -4457,27 +4647,24 @@
         <v>6</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -4486,27 +4673,27 @@
         <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>240</v>
+        <v>303</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -4515,30 +4702,27 @@
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>311</v>
+        <v>353</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -4547,59 +4731,56 @@
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>242</v>
+        <v>305</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="F100" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G100" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H100" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -4608,30 +4789,27 @@
         <v>0</v>
       </c>
       <c r="H101" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -4640,50 +4818,686 @@
         <v>0</v>
       </c>
       <c r="H102" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F103" s="1">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1">
+        <v>2</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F104" s="1">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1">
+        <v>0</v>
+      </c>
+      <c r="H104" s="1">
+        <v>6</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F105" s="1">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1">
+        <v>30</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F106" s="1">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1">
+        <v>14</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1">
+        <v>8</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="F108" s="1">
+        <v>30</v>
+      </c>
+      <c r="G108" s="1">
+        <v>60</v>
+      </c>
+      <c r="H108" s="1">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F103" s="1">
-        <v>0</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0</v>
-      </c>
-      <c r="H103" s="1">
+      <c r="B109" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F109" s="1">
+        <v>0</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0</v>
+      </c>
+      <c r="H109" s="1">
+        <v>6</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F110" s="1">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0</v>
+      </c>
+      <c r="H110" s="1">
+        <v>14</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F111" s="1">
+        <v>0</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0</v>
+      </c>
+      <c r="H111" s="1">
         <v>5</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>336</v>
+      <c r="K111" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F112" s="1">
+        <v>0</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0</v>
+      </c>
+      <c r="H112" s="1">
+        <v>6</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F113" s="1">
+        <v>0</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0</v>
+      </c>
+      <c r="H113" s="1">
+        <v>2</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F114" s="1">
+        <v>0</v>
+      </c>
+      <c r="G114" s="1">
+        <v>0</v>
+      </c>
+      <c r="H114" s="1">
+        <v>30</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F115" s="1">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0</v>
+      </c>
+      <c r="H115" s="1">
+        <v>10</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F116" s="1">
+        <v>0</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0</v>
+      </c>
+      <c r="H116" s="1">
+        <v>105</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F117" s="1">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0</v>
+      </c>
+      <c r="H117" s="1">
+        <v>8</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F118" s="1">
+        <v>360</v>
+      </c>
+      <c r="G118" s="1">
+        <v>60</v>
+      </c>
+      <c r="H118" s="1">
+        <v>1</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F119" s="1">
+        <v>0</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0</v>
+      </c>
+      <c r="H119" s="1">
+        <v>6</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F120" s="1">
+        <v>0</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0</v>
+      </c>
+      <c r="H120" s="1">
+        <v>334</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F121" s="1">
+        <v>0</v>
+      </c>
+      <c r="G121" s="1">
+        <v>0</v>
+      </c>
+      <c r="H121" s="1">
+        <v>6</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F122" s="1">
+        <v>0</v>
+      </c>
+      <c r="G122" s="1">
+        <v>0</v>
+      </c>
+      <c r="H122" s="1">
+        <v>82</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F123" s="1">
+        <v>0</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0</v>
+      </c>
+      <c r="H123" s="1">
+        <v>1278</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F124" s="1">
+        <v>0</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>90</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K103"/>
+  <autoFilter ref="A1:K124"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="1" customWidth="1"/>
@@ -4695,30 +5509,30 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>337</v>
+        <v>391</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>338</v>
+        <v>392</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>339</v>
+        <v>393</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>341</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -4726,16 +5540,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>350</v>
+        <v>408</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -4743,13 +5557,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -4757,13 +5571,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>345</v>
+        <v>399</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>351</v>
+        <v>409</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -4771,13 +5585,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>346</v>
+        <v>400</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>352</v>
+        <v>410</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -4785,13 +5599,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>352</v>
+        <v>410</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -4799,20 +5613,76 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>348</v>
+        <v>402</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
     </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4830,180 +5700,180 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>355</v>
+        <v>413</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>356</v>
+        <v>414</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>357</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>359</v>
+        <v>417</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>366</v>
+        <v>424</v>
       </c>
       <c r="D2" s="1">
-        <v>12305</v>
+        <v>12974</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>367</v>
+        <v>425</v>
       </c>
       <c r="D3" s="1">
-        <v>9394</v>
+        <v>9704</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="D4" s="1">
-        <v>26970</v>
+        <v>25093</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>362</v>
+        <v>420</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>369</v>
+        <v>427</v>
       </c>
       <c r="D5" s="1">
-        <v>12943</v>
+        <v>10508</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="D6" s="1">
-        <v>8533</v>
+        <v>7807</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>364</v>
+        <v>422</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>371</v>
+        <v>429</v>
       </c>
       <c r="D7" s="1">
-        <v>7727</v>
+        <v>8342</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>365</v>
+        <v>423</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>372</v>
+        <v>430</v>
       </c>
       <c r="D8" s="1">
-        <v>24948</v>
+        <v>25437</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>373</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>374</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>375</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>376</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="B13" s="1">
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>377</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="B14" s="1">
         <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -5014,7 +5884,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5023,94 +5893,102 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>379</v>
+        <v>437</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>380</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>381</v>
+        <v>439</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>389</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>390</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>391</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>392</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>394</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>385</v>
+        <v>442</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>395</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>396</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>397</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>398</v>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>457</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>